--- a/output/pdf_financials_xlsx/SCR.xlsx
+++ b/output/pdf_financials_xlsx/SCR.xlsx
@@ -4115,16 +4115,16 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.19</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-1.131</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.605</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-0.383</v>
       </c>
       <c r="F118" s="3" t="n">
         <v>0</v>
@@ -13684,7 +13684,11 @@
           <t>Exploration and evaluation asset expenditures 5</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E162" t="inlineStr">
         <is>
           <t>-</t>
@@ -15298,7 +15302,11 @@
           <t>Exploration and evaluation asset expenditures 6</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E191" s="5" t="n">
         <v>-0.19</v>
       </c>

--- a/output/pdf_financials_xlsx/SCR.xlsx
+++ b/output/pdf_financials_xlsx/SCR.xlsx
@@ -713,16 +713,16 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0</v>
+        <v>10.206</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0</v>
+        <v>66.51600000000001</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0</v>
+        <v>145.323</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>207.344</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0.0027141</v>
@@ -1525,7 +1525,7 @@
         <v>0</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>3.43e-05</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>3.43e-05</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0</v>
@@ -1959,7 +1959,7 @@
         <v>3.94</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>5.809999999999997e-05</v>
+        <v>2.379999999999996e-05</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>6.939999999999998e-05</v>
@@ -4304,13 +4304,13 @@
         <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.839</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-3.706</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-4.896</v>
       </c>
       <c r="F124" s="3" t="n">
         <v>0</v>
@@ -4335,13 +4335,13 @@
         <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.839</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-3.706</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-4.896</v>
       </c>
       <c r="F125" s="3" t="n">
         <v>0</v>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -14072,7 +14072,11 @@
           <t>Principal portion of lease payments 9</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -15860,7 +15864,11 @@
           <t>Principal portion of lease payments 11</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -20268,7 +20276,7 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E282" s="5" t="n">

--- a/output/pdf_financials_xlsx/SCR.xlsx
+++ b/output/pdf_financials_xlsx/SCR.xlsx
@@ -2477,10 +2477,10 @@
         <v>0</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0</v>
+        <v>0.000919</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0</v>
+        <v>0.000619</v>
       </c>
     </row>
     <row r="65">
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.000634</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.000396</v>
       </c>
     </row>
     <row r="68">
@@ -2648,13 +2648,13 @@
         <v>0</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>3.617</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>4.665</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>0</v>
+        <v>6.144</v>
       </c>
       <c r="F70" s="3" t="n">
         <v>0</v>
@@ -2679,13 +2679,13 @@
         <v>0</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>3.617</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>4.665</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>0</v>
+        <v>6.144</v>
       </c>
       <c r="F71" s="3" t="n">
         <v>0</v>
@@ -2803,13 +2803,13 @@
         <v>1.548</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>6.366</v>
+        <v>2.749</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>11.44</v>
+        <v>6.775</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>12.16</v>
+        <v>6.016</v>
       </c>
       <c r="F75" s="3" t="n">
         <v>0.0004711</v>
@@ -2960,13 +2960,13 @@
         </is>
       </c>
       <c r="C80" s="3" t="n">
-        <v>0.1359183949199487</v>
+        <v>0.1456920894413295</v>
       </c>
       <c r="D80" s="3" t="n">
-        <v>0.1508485937508801</v>
+        <v>0.1639872922170462</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>0.1937357042198664</v>
+        <v>0.2082386182575259</v>
       </c>
       <c r="F80" s="3" t="n">
         <v>0.6542049402693827</v>
@@ -4012,7 +4012,7 @@
         <v>0</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>0</v>
+        <v>-0.000928</v>
       </c>
     </row>
     <row r="115">
@@ -8090,7 +8090,11 @@
           <t>Lease liabilities 9</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E62" t="inlineStr">
         <is>
           <t>-</t>
@@ -9492,7 +9496,11 @@
           <t>Lease liabilities 11</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -10996,7 +11004,11 @@
           <t>Purchase of marketable securities 6, 18</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -13406,7 +13418,11 @@
           <t>Deferred income tax expense (recovery) 16(a)</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -14976,7 +14992,11 @@
           <t>Deferred income tax recovery 17(a)</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E185" s="5" t="n">
         <v>-0.058</v>
       </c>
